--- a/test_automation_framework/configs/creds_file.xlsx
+++ b/test_automation_framework/configs/creds_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/PycharmProjects/etl_automation_jan/test_automation_framework/configs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A908B7-4D6C-AA4F-BBC5-BE5793413CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C078F6-0BDB-5847-8A94-851CEA42BDA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28800" yWindow="600" windowWidth="28800" windowHeight="15880" xr2:uid="{65144EEF-1F90-C947-8815-970505B648B2}"/>
   </bookViews>
@@ -123,9 +123,6 @@
     <t>range</t>
   </si>
   <si>
-    <t>env</t>
-  </si>
-  <si>
     <t>SID</t>
   </si>
   <si>
@@ -157,6 +154,9 @@
   </si>
   <si>
     <t>bkbnrdx-yg92711</t>
+  </si>
+  <si>
+    <t>database_type</t>
   </si>
 </sst>
 </file>
@@ -2302,7 +2302,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2317,10 +2317,10 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2328,13 +2328,13 @@
         <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
@@ -2359,22 +2359,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>33</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
         <v>34</v>
-      </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" t="s">
-        <v>35</v>
       </c>
       <c r="G4">
         <v>1521</v>
@@ -2382,19 +2382,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
         <v>32</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>33</v>
       </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
